--- a/data/compare/launch-do-vs-ls-products.xlsx
+++ b/data/compare/launch-do-vs-ls-products.xlsx
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-14T05:27:15.662820+00:00</t>
+          <t>2026-08-14T06:28:08.493131+00:00</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1582,29 +1582,29 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>copper-bottle-pink-noble-toughts</t>
+          <t>copper-bottle-orange-light</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>copper-bottle-pink-noble-toughts</t>
+          <t>copper-bottle-orange-light</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pink &amp; Positive</t>
+          <t>Copper Bottle - Sunshine within Me</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pink &amp; Positive</t>
+          <t>Sunshine within Me</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>5778</v>
+        <v>5669</v>
       </c>
       <c r="H23" t="n">
-        <v>5663</v>
+        <v>5669</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
@@ -1624,29 +1624,29 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>copper-bottle-vintage-plain-curved</t>
+          <t>copper-bottle-pink-noble-toughts</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>copper-bottle-vintage-plain-curved</t>
+          <t>copper-bottle-pink-noble-toughts</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Curved Copper Bottles</t>
+          <t>Copper Bottle - Pink &amp; Positive</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Curved Copper Bottles</t>
+          <t>Pink &amp; Positive</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>5489</v>
+        <v>5663</v>
       </c>
       <c r="H24" t="n">
-        <v>5489</v>
+        <v>5663</v>
       </c>
       <c r="I24" t="n">
         <v>4</v>
@@ -1666,29 +1666,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>copper-bottle-with-brush-tattvamasi</t>
+          <t>copper-bottle-vintage-plain-curved</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>copper-bottle-with-brush-tattvamasi</t>
+          <t>copper-bottle-vintage-plain-curved</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tattvamasi-I am Infinite</t>
+          <t>Curved Copper Bottles</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tattvamasi-I am Infinite</t>
+          <t>Curved Copper Bottles</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>5632</v>
+        <v>5489</v>
       </c>
       <c r="H25" t="n">
-        <v>5466</v>
+        <v>5489</v>
       </c>
       <c r="I25" t="n">
         <v>4</v>
@@ -1708,29 +1708,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>copper-bottle-with-brush-true-happiness-lies-within</t>
+          <t>copper-bottle-with-brush-tattvamasi</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>copper-bottle-with-brush-true-happiness-lies-within</t>
+          <t>copper-bottle-with-brush-tattvamasi</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Happiness is Inside</t>
+          <t>Copper Bottle - Tattvamasi-I am Infinite</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Happiness is Inside</t>
+          <t>Tattvamasi-I am Infinite</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>5634</v>
+        <v>5466</v>
       </c>
       <c r="H26" t="n">
-        <v>5459</v>
+        <v>5466</v>
       </c>
       <c r="I26" t="n">
         <v>4</v>
@@ -1750,35 +1750,35 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>crystal-bowl-bag</t>
+          <t>copper-bottle-with-brush-true-happiness-lies-within</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>crystal-bowl-bag</t>
+          <t>copper-bottle-with-brush-true-happiness-lies-within</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Crystal Bowl Bag</t>
+          <t>Copper Bottle - Happiness is Inside</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Crystal Bowl Bag</t>
+          <t>Happiness is Inside</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>47081</v>
+        <v>5459</v>
       </c>
       <c r="H27" t="n">
-        <v>47081</v>
+        <v>5459</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1792,35 +1792,35 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>crystal-bowl-with-handle</t>
+          <t>crystal-bowl-bag</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>crystal-bowl-with-handle</t>
+          <t>crystal-bowl-bag</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Crystal Bowl with Handle</t>
+          <t>Crystal Bowl Bag</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Crystal Bowl with Handle</t>
+          <t>Crystal Bowl Bag</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>45661</v>
+        <v>47081</v>
       </c>
       <c r="H28" t="n">
-        <v>45661</v>
+        <v>47081</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1834,35 +1834,35 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>crystal-bowls-set-of-7</t>
+          <t>crystal-bowl-with-handle</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>crystal-bowls-set-of-7</t>
+          <t>crystal-bowl-with-handle</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Crystal Bowls - Set of 7</t>
+          <t>Crystal Bowl with Handle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Crystal Bowls - Set of 7</t>
+          <t>Crystal Bowl with Handle</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>43219</v>
+        <v>45661</v>
       </c>
       <c r="H29" t="n">
-        <v>43219</v>
+        <v>45661</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1876,35 +1876,35 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>crystal-pyramid</t>
+          <t>crystal-bowls-set-of-7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>crystal-pyramid</t>
+          <t>crystal-bowls-set-of-7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crystal Pyramid</t>
+          <t>Crystal Bowls - Set of 7</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crystal Pyramid</t>
+          <t>Crystal Bowls - Set of 7</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>45654</v>
+        <v>43219</v>
       </c>
       <c r="H30" t="n">
-        <v>45654</v>
+        <v>43219</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1918,35 +1918,35 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>djembe-drums</t>
+          <t>crystal-pyramid</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>djembe-drums</t>
+          <t>crystal-pyramid</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Djembe Drums</t>
+          <t>Crystal Pyramid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Djembe Drums</t>
+          <t>Crystal Pyramid</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>44969</v>
+        <v>45654</v>
       </c>
       <c r="H31" t="n">
-        <v>44969</v>
+        <v>45654</v>
       </c>
       <c r="I31" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1960,35 +1960,35 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>egg-shaker-with-handle</t>
+          <t>djembe-drums</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>egg-shaker-with-handle</t>
+          <t>djembe-drums</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Egg Shaker with Handle</t>
+          <t>Djembe Drums</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Egg Shaker with Handle</t>
+          <t>Djembe Drums</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>7396</v>
+        <v>44969</v>
       </c>
       <c r="H32" t="n">
-        <v>7396</v>
+        <v>44969</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -2002,35 +2002,35 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>etched-gongs</t>
+          <t>egg-shaker-with-handle</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>etched-gongs</t>
+          <t>egg-shaker-with-handle</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Etched Chau Gongs</t>
+          <t>Egg Shaker with Handle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Etched Chau Gongs</t>
+          <t>Egg Shaker with Handle</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>49115</v>
+        <v>7396</v>
       </c>
       <c r="H33" t="n">
-        <v>49115</v>
+        <v>7396</v>
       </c>
       <c r="I33" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2044,35 +2044,35 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>etched-handmade-singing-bowls</t>
+          <t>etched-gongs</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>etched-handmade-singing-bowls</t>
+          <t>etched-gongs</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Etched Handmade Singing Bowls</t>
+          <t>Etched Chau Gongs</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Etched Handmade Singing Bowls</t>
+          <t>Etched Chau Gongs</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>9795</v>
+        <v>49115</v>
       </c>
       <c r="H34" t="n">
-        <v>9795</v>
+        <v>49115</v>
       </c>
       <c r="I34" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="J34" t="n">
-        <v>78</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35">
@@ -2086,35 +2086,35 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>gong-bags</t>
+          <t>etched-handmade-singing-bowls</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>gong-bags</t>
+          <t>etched-handmade-singing-bowls</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gong Bags</t>
+          <t>Etched Handmade Singing Bowls</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gong Bags</t>
+          <t>Etched Handmade Singing Bowls</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>45152</v>
+        <v>9795</v>
       </c>
       <c r="H35" t="n">
-        <v>45152</v>
+        <v>9795</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36">
@@ -2128,35 +2128,35 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>gong-stand</t>
+          <t>gong-bags</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>gong-stand</t>
+          <t>gong-bags</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gong Stand</t>
+          <t>Gong Bags</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gong Stand</t>
+          <t>Gong Bags</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>45289</v>
+        <v>45152</v>
       </c>
       <c r="H36" t="n">
-        <v>45289</v>
+        <v>45152</v>
       </c>
       <c r="I36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2170,35 +2170,35 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>handpan-stand</t>
+          <t>gong-stand</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>handpan-stand</t>
+          <t>gong-stand</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Handpan Stand</t>
+          <t>Gong Stand</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Handpan Stand</t>
+          <t>Gong Stand</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>46907</v>
+        <v>45289</v>
       </c>
       <c r="H37" t="n">
-        <v>46907</v>
+        <v>45289</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -2212,29 +2212,29 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>hanging-bowls-zen-drops</t>
+          <t>handpan-stand</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>hanging-bowls-zen-drops</t>
+          <t>handpan-stand</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hanging Bowls/Zen Drops</t>
+          <t>Handpan Stand</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hanging Bowls/Zen Drops</t>
+          <t>Handpan Stand</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>45113</v>
+        <v>46907</v>
       </c>
       <c r="H38" t="n">
-        <v>45113</v>
+        <v>46907</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -2254,35 +2254,35 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>harmonium</t>
+          <t>hanging-bowls-zen-drops</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>harmonium</t>
+          <t>hanging-bowls-zen-drops</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Harmonium</t>
+          <t>Hanging Bowls/Zen Drops</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harmonium</t>
+          <t>Hanging Bowls/Zen Drops</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>44972</v>
+        <v>45113</v>
       </c>
       <c r="H39" t="n">
-        <v>44972</v>
+        <v>45113</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2296,35 +2296,35 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>kenari-bracelet</t>
+          <t>harmonium</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>kenari-bracelet</t>
+          <t>harmonium</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kenari Bracelet</t>
+          <t>Harmonium</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kenari Bracelet</t>
+          <t>Harmonium</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>42323</v>
+        <v>44972</v>
       </c>
       <c r="H40" t="n">
-        <v>42323</v>
+        <v>44972</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2338,35 +2338,35 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>kenari-chimes</t>
+          <t>kenari-bracelet</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>kenari-chimes</t>
+          <t>kenari-bracelet</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kenari Chimes</t>
+          <t>Kenari Bracelet</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kenari Chimes - Small &amp; Large</t>
+          <t>Kenari Bracelet</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>45197</v>
+        <v>42323</v>
       </c>
       <c r="H41" t="n">
-        <v>45197</v>
+        <v>42323</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2380,35 +2380,35 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>large-tuning-fork</t>
+          <t>kenari-chimes</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>large-tuning-fork</t>
+          <t>kenari-chimes</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>DNA Tuning Fork</t>
+          <t>Kenari Chimes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>DNA Tuning Fork</t>
+          <t>Kenari Chimes - Small &amp; Large</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>49817</v>
+        <v>45197</v>
       </c>
       <c r="H42" t="n">
-        <v>49817</v>
+        <v>45197</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2422,32 +2422,32 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>mayura-morchang-set</t>
+          <t>large-tuning-fork</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>mayura-morchang-set</t>
+          <t>large-tuning-fork</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mayura Morchang Set</t>
+          <t>DNA Tuning Fork</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mayura Morchang Set</t>
+          <t>DNA Tuning Fork</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>48856</v>
+        <v>49817</v>
       </c>
       <c r="H43" t="n">
-        <v>48856</v>
+        <v>49817</v>
       </c>
       <c r="I43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>4</v>
@@ -2464,35 +2464,35 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>native-american-style-flute-handcrafted-wooden-melody-maker</t>
+          <t>mayura-morchang-set</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>native-american-style-flute-handcrafted-wooden-melody-maker</t>
+          <t>mayura-morchang-set</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Native American Flute - Single Small</t>
+          <t>Mayura Morchang Set</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Native American Style Flutes</t>
+          <t>Mayura Morchang Set</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>48428</v>
+        <v>48856</v>
       </c>
       <c r="H44" t="n">
-        <v>48428</v>
+        <v>48856</v>
       </c>
       <c r="I44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -2506,35 +2506,35 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ocean-drums</t>
+          <t>native-american-style-flute-handcrafted-wooden-melody-maker</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ocean-drums</t>
+          <t>native-american-style-flute-handcrafted-wooden-melody-maker</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ocean Drums</t>
+          <t>Native American Flute - Single Small</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ocean Drums</t>
+          <t>Native American Style Flutes</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>9529</v>
+        <v>48428</v>
       </c>
       <c r="H45" t="n">
-        <v>9529</v>
+        <v>48428</v>
       </c>
       <c r="I45" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J45" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -2548,35 +2548,35 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>plain-yoga-mats</t>
+          <t>ocean-drums</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>plain-yoga-mats</t>
+          <t>ocean-drums</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Plain Yoga Mats</t>
+          <t>Ocean Drums</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plain Yoga Mats</t>
+          <t>Ocean Drums</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>46220</v>
+        <v>9529</v>
       </c>
       <c r="H46" t="n">
-        <v>46220</v>
+        <v>9529</v>
       </c>
       <c r="I46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
@@ -2590,35 +2590,35 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>pulse-tubes</t>
+          <t>plain-yoga-mats</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>pulse-tubes</t>
+          <t>plain-yoga-mats</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pulse Tubes</t>
+          <t>Plain Yoga Mats</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pulse Tubes</t>
+          <t>Plain Yoga Mats</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>48512</v>
+        <v>46220</v>
       </c>
       <c r="H47" t="n">
-        <v>48512</v>
+        <v>46220</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -2632,29 +2632,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>s-shaped-didgeridoo</t>
+          <t>pulse-tubes</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>s-shaped-didgeridoo</t>
+          <t>pulse-tubes</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>S-Shaped Didgeridoo</t>
+          <t>Pulse Tubes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>S-Shaped Didgeridoo</t>
+          <t>Pulse Tubes</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>7307</v>
+        <v>48512</v>
       </c>
       <c r="H48" t="n">
-        <v>7307</v>
+        <v>48512</v>
       </c>
       <c r="I48" t="n">
         <v>3</v>
@@ -2674,29 +2674,29 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>shankh-conch</t>
+          <t>s-shaped-didgeridoo</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>shankh-conch</t>
+          <t>s-shaped-didgeridoo</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shankh/Conch</t>
+          <t>S-Shaped Didgeridoo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shankh/Conch</t>
+          <t>S-Shaped Didgeridoo</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>45449</v>
+        <v>7307</v>
       </c>
       <c r="H49" t="n">
-        <v>45449</v>
+        <v>7307</v>
       </c>
       <c r="I49" t="n">
         <v>3</v>
@@ -2716,32 +2716,32 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>shruti-box</t>
+          <t>shankh-conch</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>shruti-box</t>
+          <t>shankh-conch</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shruti Box</t>
+          <t>Shankh/Conch</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shruti Box</t>
+          <t>Shankh/Conch</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>44970</v>
+        <v>45449</v>
       </c>
       <c r="H50" t="n">
-        <v>44970</v>
+        <v>45449</v>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J50" t="n">
         <v>3</v>
@@ -2758,35 +2758,35 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>shruti-box-pedal</t>
+          <t>shruti-box</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>shruti-box-pedal</t>
+          <t>shruti-box</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shruti Box Pedal</t>
+          <t>Shruti Box</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Shruti Box Pedal</t>
+          <t>Shruti Box</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>51090</v>
+        <v>44970</v>
       </c>
       <c r="H51" t="n">
-        <v>51090</v>
+        <v>44970</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -2800,35 +2800,35 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>singing-bowl-bags</t>
+          <t>shruti-box-pedal</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>singing-bowl-bags</t>
+          <t>shruti-box-pedal</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Singing Bowl Bags</t>
+          <t>Shruti Box Pedal</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Singing Bowl Bags</t>
+          <t>Shruti Box Pedal</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>45127</v>
+        <v>51090</v>
       </c>
       <c r="H52" t="n">
-        <v>45127</v>
+        <v>51090</v>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2842,35 +2842,35 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>singing-bowl-set-g-a-b</t>
+          <t>singing-bowl-bags</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>singing-bowl-set-g-a-b</t>
+          <t>singing-bowl-bags</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Singing Bowl Head Set – G, A, B</t>
+          <t>Singing Bowl Bags</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Singing Bowl Head Set – G, A, B</t>
+          <t>Singing Bowl Bags</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>49832</v>
+        <v>45127</v>
       </c>
       <c r="H53" t="n">
-        <v>49832</v>
+        <v>45127</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -2884,29 +2884,29 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>singing-bowl-with-handle</t>
+          <t>singing-bowl-set-g-a-b</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>singing-bowl-with-handle</t>
+          <t>singing-bowl-set-g-a-b</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Singing Bowl with Handle</t>
+          <t>Singing Bowl Head Set – G, A, B</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Singing Bowl with Handle</t>
+          <t>Singing Bowl Head Set – G, A, B</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>48931</v>
+        <v>49832</v>
       </c>
       <c r="H54" t="n">
-        <v>48931</v>
+        <v>49832</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
@@ -2926,35 +2926,35 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>singing-bowls-with-sacred-mantra-printed</t>
+          <t>singing-bowl-with-handle</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>singing-bowls-with-sacred-mantra-printed</t>
+          <t>singing-bowl-with-handle</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Singing Bowls with Sacred Mantra Printed</t>
+          <t>Singing Bowl with Handle</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Singing Bowls with Sacred Mantra Printed</t>
+          <t>Singing Bowl with Handle</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>6807</v>
+        <v>48931</v>
       </c>
       <c r="H55" t="n">
-        <v>6807</v>
+        <v>48931</v>
       </c>
       <c r="I55" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2968,35 +2968,35 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>sleigh-bells-wooden-jingle-stick</t>
+          <t>singing-bowls-with-sacred-mantra-printed</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>sleigh-bells-wooden-jingle-stick</t>
+          <t>singing-bowls-with-sacred-mantra-printed</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sleigh Bells Wooden Jingle Stick</t>
+          <t>Singing Bowls with Sacred Mantra Printed</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sleigh Bells Wooden Jingle Stick</t>
+          <t>Singing Bowls with Sacred Mantra Printed</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>50608</v>
+        <v>6807</v>
       </c>
       <c r="H56" t="n">
-        <v>50608</v>
+        <v>6807</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -3010,29 +3010,29 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>solar-bell</t>
+          <t>sleigh-bells-wooden-jingle-stick</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>solar-bell</t>
+          <t>sleigh-bells-wooden-jingle-stick</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Solar Bell</t>
+          <t>Sleigh Bells Wooden Jingle Stick</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Solar Bell</t>
+          <t>Sleigh Bells Wooden Jingle Stick</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>49816</v>
+        <v>50608</v>
       </c>
       <c r="H57" t="n">
-        <v>49816</v>
+        <v>50608</v>
       </c>
       <c r="I57" t="n">
         <v>1</v>
@@ -3052,35 +3052,35 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>spiral-snake-didgeridoo</t>
+          <t>solar-bell</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>spiral-snake-didgeridoo</t>
+          <t>solar-bell</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Spiral/Snake Didgeridoo</t>
+          <t>Solar Bell</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spiral/Snake Didgeridoo</t>
+          <t>Solar Bell</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>7324</v>
+        <v>49816</v>
       </c>
       <c r="H58" t="n">
-        <v>7324</v>
+        <v>49816</v>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3094,29 +3094,29 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>stainless-steel-straws</t>
+          <t>spiral-snake-didgeridoo</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>stainless-steel-straws</t>
+          <t>spiral-snake-didgeridoo</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stainless Steel Straws</t>
+          <t>Spiral/Snake Didgeridoo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stainless Steel Straws</t>
+          <t>Spiral/Snake Didgeridoo</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>6505</v>
+        <v>7324</v>
       </c>
       <c r="H59" t="n">
-        <v>6505</v>
+        <v>7324</v>
       </c>
       <c r="I59" t="n">
         <v>2</v>
@@ -3136,29 +3136,29 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>swinging-chimes</t>
+          <t>stainless-steel-straws</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>swinging-chimes</t>
+          <t>stainless-steel-straws</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Swinging Chimes</t>
+          <t>Stainless Steel Straws</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Swinging Chimes</t>
+          <t>Stainless Steel Straws</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>10345</v>
+        <v>6505</v>
       </c>
       <c r="H60" t="n">
-        <v>10345</v>
+        <v>6505</v>
       </c>
       <c r="I60" t="n">
         <v>2</v>
@@ -3178,35 +3178,35 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>the-head-bowl</t>
+          <t>swinging-chimes</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>the-head-bowl</t>
+          <t>swinging-chimes</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>The Head Bowl</t>
+          <t>Swinging Chimes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>The Head Bowl</t>
+          <t>Swinging Chimes</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>45518</v>
+        <v>10345</v>
       </c>
       <c r="H61" t="n">
-        <v>45518</v>
+        <v>10345</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3220,29 +3220,29 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>third-eye-chakra-singing-bowl</t>
+          <t>the-head-bowl</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>third-eye-chakra-singing-bowl</t>
+          <t>the-head-bowl</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Third Eye Chakra Singing Bowl</t>
+          <t>The Head Bowl</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Third Eye Chakra Singing Bowl</t>
+          <t>The Head Bowl</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>45477</v>
+        <v>45518</v>
       </c>
       <c r="H62" t="n">
-        <v>45477</v>
+        <v>45518</v>
       </c>
       <c r="I62" t="n">
         <v>1</v>
@@ -3262,35 +3262,35 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>tingsha-bell</t>
+          <t>third-eye-chakra-singing-bowl</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>tingsha-bell</t>
+          <t>third-eye-chakra-singing-bowl</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Tingsha Bell</t>
+          <t>Third Eye Chakra Singing Bowl</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tingsha Bell</t>
+          <t>Third Eye Chakra Singing Bowl</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>5763</v>
+        <v>45477</v>
       </c>
       <c r="H63" t="n">
-        <v>5763</v>
+        <v>45477</v>
       </c>
       <c r="I63" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -3304,35 +3304,35 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>tuning-forks-7-chakra-set</t>
+          <t>tingsha-bell</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>tuning-forks-7-chakra-set</t>
+          <t>tingsha-bell</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tuning Forks 7 Chakra Set</t>
+          <t>Tingsha Bell</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tuning Forks 7 Chakra Set</t>
+          <t>Tingsha Bell</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>48193</v>
+        <v>5763</v>
       </c>
       <c r="H64" t="n">
-        <v>48193</v>
+        <v>5763</v>
       </c>
       <c r="I64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J64" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -3346,35 +3346,35 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>tuning-forks-solfeggio-set</t>
+          <t>tuning-forks-7-chakra-set</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>tuning-forks-solfeggio-set</t>
+          <t>tuning-forks-7-chakra-set</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tuning Forks Solfeggio Set</t>
+          <t>Tuning Forks 7 Chakra Set</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tuning Forks Solfeggio Set</t>
+          <t>Tuning Forks 7 Chakra Set</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>48202</v>
+        <v>48193</v>
       </c>
       <c r="H65" t="n">
-        <v>48202</v>
+        <v>48193</v>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
@@ -3388,35 +3388,35 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>universal-bowl</t>
+          <t>tuning-forks-solfeggio-set</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>universal-bowl</t>
+          <t>tuning-forks-solfeggio-set</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Universal Bowl</t>
+          <t>Tuning Forks Solfeggio Set</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Handmade Universal Bowl for Sound Healing</t>
+          <t>Tuning Forks Solfeggio Set</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>8143</v>
+        <v>48202</v>
       </c>
       <c r="H66" t="n">
-        <v>8143</v>
+        <v>48202</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -3430,35 +3430,35 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>wind-chimes</t>
+          <t>universal-bowl</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>wind-chimes</t>
+          <t>universal-bowl</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Wind Chimes</t>
+          <t>Universal Bowl</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wind Chimes</t>
+          <t>Handmade Universal Bowl for Sound Healing</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>50420</v>
+        <v>8143</v>
       </c>
       <c r="H67" t="n">
-        <v>50420</v>
+        <v>8143</v>
       </c>
       <c r="I67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3472,35 +3472,35 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>wooden-finger-castanet</t>
+          <t>wind-chimes</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>wooden-finger-castanet</t>
+          <t>wind-chimes</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Wooden Finger Castanet</t>
+          <t>Wind Chimes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wooden Finger Castanet</t>
+          <t>Wind Chimes</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>50579</v>
+        <v>50420</v>
       </c>
       <c r="H68" t="n">
-        <v>50579</v>
+        <v>50420</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69">
@@ -3514,35 +3514,35 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>wooden-guiro</t>
+          <t>wooden-finger-castanet</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>wooden-guiro</t>
+          <t>wooden-finger-castanet</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Wooden Guiro</t>
+          <t>Wooden Finger Castanet</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wooden Guiro</t>
+          <t>Wooden Finger Castanet</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>50572</v>
+        <v>50579</v>
       </c>
       <c r="H69" t="n">
-        <v>50572</v>
+        <v>50579</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -3556,35 +3556,35 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>wooden-hand-taal-khartal</t>
+          <t>wooden-guiro</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>wooden-hand-taal-khartal</t>
+          <t>wooden-guiro</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Wooden Hand Khartal/Jingles</t>
+          <t>Wooden Guiro</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wooden Hand Khartal/Jingles</t>
+          <t>Wooden Guiro</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>50964</v>
+        <v>50572</v>
       </c>
       <c r="H70" t="n">
-        <v>50964</v>
+        <v>50572</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
       </c>
       <c r="J70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -3598,35 +3598,35 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>wooden-mallets-for-singing-bowls</t>
+          <t>wooden-hand-taal-khartal</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>wooden-mallets-for-singing-bowls</t>
+          <t>wooden-hand-taal-khartal</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Wooden Mallets for Singing Bowls</t>
+          <t>Wooden Hand Khartal/Jingles</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wooden Mallets for Singing Bowls</t>
+          <t>Wooden Hand Khartal/Jingles</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>6978</v>
+        <v>50964</v>
       </c>
       <c r="H71" t="n">
-        <v>6978</v>
+        <v>50964</v>
       </c>
       <c r="I71" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -3640,34 +3640,76 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
+          <t>wooden-mallets-for-singing-bowls</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>wooden-mallets-for-singing-bowls</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Wooden Mallets for Singing Bowls</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Wooden Mallets for Singing Bowls</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>6978</v>
+      </c>
+      <c r="H72" t="n">
+        <v>6978</v>
+      </c>
+      <c r="I72" t="n">
+        <v>17</v>
+      </c>
+      <c r="J72" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>exact_slug</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>100</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
           <t>yoga-blanket</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>yoga-blanket</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Yoga Blanket</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Yoga Blanket made from Organic Cotton</t>
         </is>
       </c>
-      <c r="G72" t="n">
+      <c r="G73" t="n">
         <v>6668</v>
       </c>
-      <c r="H72" t="n">
+      <c r="H73" t="n">
         <v>6668</v>
       </c>
-      <c r="I72" t="n">
+      <c r="I73" t="n">
         <v>3</v>
       </c>
-      <c r="J72" t="n">
+      <c r="J73" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3682,7 +3724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5776,35 +5818,35 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>sunshine-within-me-artistic-design</t>
+          <t>teak-wood-stainless-steel-xylophone</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>copper-bottle-orange-light</t>
+          <t>mini-teak-wood-and-stainless-steel-xylophone</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sunshine within Me (Artistic Design)</t>
+          <t>Teak Wood - Stainless Steel Xylophone</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sunshine within Me</t>
+          <t>Teak Wood - Stainless Steel Xylophone</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>5669</v>
+        <v>7443</v>
       </c>
       <c r="H50" t="n">
-        <v>5669</v>
+        <v>7443</v>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -5818,35 +5860,35 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>teak-wood-stainless-steel-xylophone</t>
+          <t>the-four-bowl-set-root-heart-third-eye-and-universal</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>mini-teak-wood-and-stainless-steel-xylophone</t>
+          <t>the-essential-set</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Teak Wood - Stainless Steel Xylophone</t>
+          <t>The Four Bowl Set - Root, Heart, Third Eye and Universal</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Teak Wood - Stainless Steel Xylophone</t>
+          <t>The Four Bowl Set - Root, Heart, Third Eye and Universal</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>7443</v>
+        <v>45334</v>
       </c>
       <c r="H51" t="n">
-        <v>7443</v>
+        <v>45334</v>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -5860,29 +5902,29 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>the-four-bowl-set-root-heart-third-eye-and-universal</t>
+          <t>the-three-bowl-set-root-heart-and-third-eye</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>the-essential-set</t>
+          <t>the-beginner-set</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>The Four Bowl Set - Root, Heart, Third Eye and Universal</t>
+          <t>The Three Bowl Set - Root, Heart and Third Eye</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>The Four Bowl Set - Root, Heart, Third Eye and Universal</t>
+          <t>The Three Bowl Set - Root, Heart and Third Eye</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>45334</v>
+        <v>45327</v>
       </c>
       <c r="H52" t="n">
-        <v>45334</v>
+        <v>45327</v>
       </c>
       <c r="I52" t="n">
         <v>1</v>
@@ -5902,35 +5944,35 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>the-three-bowl-set-root-heart-and-third-eye</t>
+          <t>thunder-tube-basic-edition</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>the-beginner-set</t>
+          <t>thunder-tube</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>The Three Bowl Set - Root, Heart and Third Eye</t>
+          <t>Thunder Tube - Basic Edition</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>The Three Bowl Set - Root, Heart and Third Eye</t>
+          <t>Thunder Tube - Basic Edition</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>45327</v>
+        <v>7317</v>
       </c>
       <c r="H53" t="n">
-        <v>45327</v>
+        <v>7317</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -5944,35 +5986,35 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>thunder-tube-basic-edition</t>
+          <t>tibetan-buddhist-bell</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>thunder-tube</t>
+          <t>sarveda-buddhist-bell</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Thunder Tube - Basic Edition</t>
+          <t>Tibetan Buddhist Bell</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Thunder Tube - Basic Edition</t>
+          <t>Tibetan Buddhist Bell</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>7317</v>
+        <v>6973</v>
       </c>
       <c r="H54" t="n">
-        <v>7317</v>
+        <v>6973</v>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -5986,35 +6028,35 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>tibetan-buddhist-bell</t>
+          <t>tounge-cleaner</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>sarveda-buddhist-bell</t>
+          <t>copper-tongue-cleaner</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tibetan Buddhist Bell</t>
+          <t>Tounge Cleaner</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tibetan Buddhist Bell</t>
+          <t>Copper Tongue Cleaner</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>6973</v>
+        <v>5042</v>
       </c>
       <c r="H55" t="n">
-        <v>6973</v>
+        <v>5042</v>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
@@ -6028,35 +6070,35 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>tounge-cleaner</t>
+          <t>triad-crystal-bowl-set</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>copper-tongue-cleaner</t>
+          <t>ceg-crystal-singing-bowl-set</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tounge Cleaner</t>
+          <t>Triad Crystal Bowl Set</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Copper Tongue Cleaner</t>
+          <t>Triad Crystal Bowl Set</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>5042</v>
+        <v>45668</v>
       </c>
       <c r="H56" t="n">
-        <v>5042</v>
+        <v>45668</v>
       </c>
       <c r="I56" t="n">
         <v>3</v>
       </c>
       <c r="J56" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -6070,29 +6112,29 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>triad-crystal-bowl-set</t>
+          <t>tuning-fork-activators</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ceg-crystal-singing-bowl-set</t>
+          <t>tuning-forks-activators</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Triad Crystal Bowl Set</t>
+          <t>Tuning Fork Activators</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Triad Crystal Bowl Set</t>
+          <t>Tuning Fork Activators</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>45668</v>
+        <v>48133</v>
       </c>
       <c r="H57" t="n">
-        <v>45668</v>
+        <v>48133</v>
       </c>
       <c r="I57" t="n">
         <v>3</v>
@@ -6112,29 +6154,29 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>tuning-fork-activators</t>
+          <t>tuning-fork-extensions</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tuning-forks-activators</t>
+          <t>tuning-forks-extensions</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tuning Fork Activators</t>
+          <t>Tuning Fork Extensions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tuning Fork Activators</t>
+          <t>Tuning Fork Extensions</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>48133</v>
+        <v>48135</v>
       </c>
       <c r="H58" t="n">
-        <v>48133</v>
+        <v>48135</v>
       </c>
       <c r="I58" t="n">
         <v>3</v>
@@ -6154,35 +6196,35 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>tuning-fork-extensions</t>
+          <t>tuning-fork-single-weighted-unweighted</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tuning-forks-extensions</t>
+          <t>sarveda-tuning-forks</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tuning Fork Extensions</t>
+          <t>Tuning Fork - Single Weighted &amp; Unweighted</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tuning Fork Extensions</t>
+          <t>Tuning Fork - Single Weighted &amp; Unweighted</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>48135</v>
+        <v>9713</v>
       </c>
       <c r="H59" t="n">
-        <v>48135</v>
+        <v>9713</v>
       </c>
       <c r="I59" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60">
@@ -6196,35 +6238,35 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>tuning-fork-single-weighted-unweighted</t>
+          <t>tuning-forks-gem-feet</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>sarveda-tuning-forks</t>
+          <t>tuning-forks-gem-foot</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tuning Fork - Single Weighted &amp; Unweighted</t>
+          <t>Tuning Forks Gem Feet</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tuning Fork - Single Weighted &amp; Unweighted</t>
+          <t>Tuning Forks Gem Feet</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>9713</v>
+        <v>48136</v>
       </c>
       <c r="H60" t="n">
-        <v>9713</v>
+        <v>48136</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J60" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61">
@@ -6238,35 +6280,35 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>tuning-forks-gem-feet</t>
+          <t>vibroacoustic-therapy-bowls-universal-belly-and-head</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tuning-forks-gem-foot</t>
+          <t>sarveda-handcrafted-zen-singing-bowl</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tuning Forks Gem Feet</t>
+          <t>Vibroacoustic Therapy Bowls - Universal, Belly and Head</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tuning Forks Gem Feet</t>
+          <t>Vibroacoustic Therapy Bowls - Universal, Belly and Head</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>48136</v>
+        <v>8040</v>
       </c>
       <c r="H61" t="n">
-        <v>48136</v>
+        <v>8040</v>
       </c>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -6280,35 +6322,35 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>vibroacoustic-therapy-bowls-universal-belly-and-head</t>
+          <t>wind-gong-etched</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>sarveda-handcrafted-zen-singing-bowl</t>
+          <t>engraved-flat-wind-tibetan-gong-for-meditation-sound-therapy</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vibroacoustic Therapy Bowls - Universal, Belly and Head</t>
+          <t>Wind Gong - Etched</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vibroacoustic Therapy Bowls - Universal, Belly and Head</t>
+          <t>Etched Wind Gong</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>8040</v>
+        <v>8846</v>
       </c>
       <c r="H62" t="n">
-        <v>8040</v>
+        <v>8846</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="J62" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63">
@@ -6322,35 +6364,35 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>wind-gong-etched</t>
+          <t>wind-gong-plain</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>engraved-flat-wind-tibetan-gong-for-meditation-sound-therapy</t>
+          <t>plain-flat-wind-tibetan-gong-for-meditation-sound-therapy</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Wind Gong - Etched</t>
+          <t>Wind Gong - Plain</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Etched Wind Gong</t>
+          <t>Plain/Wind Tibetan Gong</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>8846</v>
+        <v>8833</v>
       </c>
       <c r="H63" t="n">
-        <v>8846</v>
+        <v>8833</v>
       </c>
       <c r="I63" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="J63" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
@@ -6364,35 +6406,35 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>wind-gong-plain</t>
+          <t>wooden-frog</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>plain-flat-wind-tibetan-gong-for-meditation-sound-therapy</t>
+          <t>musical-wooden-frog</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Wind Gong - Plain</t>
+          <t>Wooden Frog</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Plain/Wind Tibetan Gong</t>
+          <t>Musical Wooden Frog</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>8833</v>
+        <v>7456</v>
       </c>
       <c r="H64" t="n">
-        <v>8833</v>
+        <v>7456</v>
       </c>
       <c r="I64" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -6406,35 +6448,35 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>wooden-frog</t>
+          <t>wooden-maracas-shakers-plain-dot-painted</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>musical-wooden-frog</t>
+          <t>wooden-maracas-shaker-handheld-shaker</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Wooden Frog</t>
+          <t>Wooden Maracas Shakers | Plain &amp; Dot Painted</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Musical Wooden Frog</t>
+          <t>Wooden Maracas Shakers | Plain &amp; Dot Painted</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>7456</v>
+        <v>7542</v>
       </c>
       <c r="H65" t="n">
-        <v>7456</v>
+        <v>7542</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -6448,35 +6490,35 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>wooden-maracas-shakers-plain-dot-painted</t>
+          <t>wooden-stand-for-tuning-forks</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>wooden-maracas-shaker-handheld-shaker</t>
+          <t>handcrafted-wooden-stand-for-tuning-forks</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Wooden Maracas Shakers | Plain &amp; Dot Painted</t>
+          <t>Wooden Stand for Tuning Forks</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wooden Maracas Shakers | Plain &amp; Dot Painted</t>
+          <t>Wooden Stand for Tuning Forks</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>7542</v>
+        <v>48229</v>
       </c>
       <c r="H66" t="n">
-        <v>7542</v>
+        <v>48229</v>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -6490,35 +6532,35 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>wooden-stand-for-tuning-forks</t>
+          <t>wooden-tambourines</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>handcrafted-wooden-stand-for-tuning-forks</t>
+          <t>wooden-tambourine-half-moon-2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Wooden Stand for Tuning Forks</t>
+          <t>Wooden Tambourines</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wooden Stand for Tuning Forks</t>
+          <t>Wooden Tambourines</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>48229</v>
+        <v>7478</v>
       </c>
       <c r="H67" t="n">
-        <v>48229</v>
+        <v>7478</v>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -6532,35 +6574,35 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>wooden-tambourines</t>
+          <t>yoga-belt-strap</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>wooden-tambourine-half-moon-2</t>
+          <t>yoga-strap</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Wooden Tambourines</t>
+          <t>Yoga Belt/Strap</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wooden Tambourines</t>
+          <t>Yoga Belt/Strap for Sturdy Grip</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>7478</v>
+        <v>6530</v>
       </c>
       <c r="H68" t="n">
-        <v>7478</v>
+        <v>6530</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -6574,35 +6616,35 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>yoga-belt-strap</t>
+          <t>yoga-mats-lotus</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>yoga-strap</t>
+          <t>lotus-yoga-mat</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Yoga Belt/Strap</t>
+          <t>Yoga Mats-Lotus</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Yoga Belt/Strap for Sturdy Grip</t>
+          <t>Lotus Yoga Mat</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>6530</v>
+        <v>46171</v>
       </c>
       <c r="H69" t="n">
-        <v>6530</v>
+        <v>46171</v>
       </c>
       <c r="I69" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J69" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70">
@@ -6616,35 +6658,35 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>yoga-mats-lotus</t>
+          <t>zabuton-cushion</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>lotus-yoga-mat</t>
+          <t>sarveda-zabuton-cushion</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Yoga Mats-Lotus</t>
+          <t>Zabuton Cushion</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lotus Yoga Mat</t>
+          <t>Zabuton Cushion for Meditation</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>46171</v>
+        <v>6780</v>
       </c>
       <c r="H70" t="n">
-        <v>46171</v>
+        <v>6780</v>
       </c>
       <c r="I70" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J70" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -6658,29 +6700,29 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>zabuton-cushion</t>
+          <t>zafu-meditation-cushion-lotus-embroidery</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>sarveda-zabuton-cushion</t>
+          <t>zafu-meditation-cushion-with-lotus-embroidery</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Zabuton Cushion</t>
+          <t>Zafu Meditation Cushion - Lotus Embroidery</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Zabuton Cushion for Meditation</t>
+          <t>Zafu Meditation Cushion Lotus - Embroidery Filled with Cotton</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>6780</v>
+        <v>9278</v>
       </c>
       <c r="H71" t="n">
-        <v>6780</v>
+        <v>9278</v>
       </c>
       <c r="I71" t="n">
         <v>5</v>
@@ -6700,35 +6742,35 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>zafu-meditation-cushion-lotus-embroidery</t>
+          <t>zafu-meditation-cushion-plain</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>zafu-meditation-cushion-with-lotus-embroidery</t>
+          <t>sarveda-zafu-round</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Zafu Meditation Cushion - Lotus Embroidery</t>
+          <t>Zafu Meditation Cushion - Plain</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Zafu Meditation Cushion Lotus - Embroidery Filled with Cotton</t>
+          <t>Zafu Meditation Cushion Plain Filled with Cotton</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>9278</v>
+        <v>6711</v>
       </c>
       <c r="H72" t="n">
-        <v>9278</v>
+        <v>6711</v>
       </c>
       <c r="I72" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73">
@@ -6742,35 +6784,35 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>zafu-meditation-cushion-plain</t>
+          <t>zafu-zabuton-combo-lotus-embroidery</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>sarveda-zafu-round</t>
+          <t>zafu-zabuton-meditation-cushion-combo-with-lotus-embroidery</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Zafu Meditation Cushion - Plain</t>
+          <t>Zafu &amp; Zabuton Combo - Lotus Embroidery</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Zafu Meditation Cushion Plain Filled with Cotton</t>
+          <t>Zafu &amp; Zabuton Meditation Cushion Combo - Lotus Embroidery</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>6711</v>
+        <v>9312</v>
       </c>
       <c r="H73" t="n">
-        <v>6711</v>
+        <v>9312</v>
       </c>
       <c r="I73" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J73" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -6784,35 +6826,35 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>zafu-zabuton-combo-lotus-embroidery</t>
+          <t>zafu-zabuton-combo-plain</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>zafu-zabuton-meditation-cushion-combo-with-lotus-embroidery</t>
+          <t>sarveda-zafu-zabuton-meditation-cushion-combo</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Zafu &amp; Zabuton Combo - Lotus Embroidery</t>
+          <t>Zafu &amp; Zabuton Combo - Plain</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Zafu &amp; Zabuton Meditation Cushion Combo - Lotus Embroidery</t>
+          <t>Zafu &amp; Zabuton Meditation Cushion Combo</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>9312</v>
+        <v>7177</v>
       </c>
       <c r="H74" t="n">
-        <v>9312</v>
+        <v>7177</v>
       </c>
       <c r="I74" t="n">
         <v>5</v>
       </c>
       <c r="J74" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -6826,76 +6868,34 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>zafu-zabuton-combo-plain</t>
+          <t>zen-meditation-bench</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>sarveda-zafu-zabuton-meditation-cushion-combo</t>
+          <t>ergonomic-meditation-bench</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Zafu &amp; Zabuton Combo - Plain</t>
+          <t>Zen Meditation Bench</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Zafu &amp; Zabuton Meditation Cushion Combo</t>
+          <t>Zen Meditation Bench</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>7177</v>
+        <v>9763</v>
       </c>
       <c r="H75" t="n">
-        <v>7177</v>
+        <v>9763</v>
       </c>
       <c r="I75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>exact_woo_id</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>100</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>zen-meditation-bench</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>ergonomic-meditation-bench</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Zen Meditation Bench</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Zen Meditation Bench</t>
-        </is>
-      </c>
-      <c r="G76" t="n">
-        <v>9763</v>
-      </c>
-      <c r="H76" t="n">
-        <v>9763</v>
-      </c>
-      <c r="I76" t="n">
-        <v>3</v>
-      </c>
-      <c r="J76" t="n">
         <v>3</v>
       </c>
     </row>
